--- a/data/trans_dic/P70D_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P70D_R-Provincia-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con capacidad laboral &lt;=6 (Likert 0 a 10)</t>
+          <t>Población con capacidad laboral &lt;=6 (Likert 0 a 10) (tasa de respuesta: 99,65%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,8; 5,31</t>
+          <t>0,66; 5,23</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,56</t>
+          <t>0,0; 1,47</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,44; 2,9</t>
+          <t>0,43; 3,17</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,17; 8,64</t>
+          <t>1,86; 7,75</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,03; 9,74</t>
+          <t>3,06; 9,23</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,89; 7,39</t>
+          <t>2,89; 7,13</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,91; 10,12</t>
+          <t>2,8; 10,21</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,72; 15,68</t>
+          <t>5,63; 15,26</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,01; 10,64</t>
+          <t>5,1; 11,17</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,87; 15,92</t>
+          <t>4,44; 15,36</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,27; 11,51</t>
+          <t>2,07; 11,2</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,79; 10,47</t>
+          <t>3,89; 11,01</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,39; 7,3</t>
+          <t>1,25; 7,35</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,93; 4,66</t>
+          <t>0,9; 4,69</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,53; 4,93</t>
+          <t>1,49; 4,93</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5,99; 15,77</t>
+          <t>6,06; 16,31</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7,02; 18,35</t>
+          <t>7,47; 18,04</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7,93; 15,17</t>
+          <t>7,82; 14,96</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,34; 4,51</t>
+          <t>0,58; 4,03</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,21; 4,07</t>
+          <t>1,2; 4,24</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,15; 3,51</t>
+          <t>1,17; 3,65</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,65; 4,73</t>
+          <t>0,78; 4,9</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>6,68; 17,31</t>
+          <t>6,45; 16,52</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2,08; 7,39</t>
+          <t>1,87; 7,22</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,53; 4,92</t>
+          <t>2,56; 5,15</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>4,6; 7,39</t>
+          <t>4,49; 7,2</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3,66; 5,72</t>
+          <t>3,63; 5,6</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con capacidad laboral &lt;=6 (Likert 0 a 10)</t>
+          <t>Población con capacidad laboral &lt;=6 (Likert 0 a 10) (tasa de respuesta: 99,65%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1548; 10316</t>
+          <t>1287; 10161</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 2247</t>
+          <t>0; 2125</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1473; 9807</t>
+          <t>1461; 10727</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5365; 21309</t>
+          <t>4587; 19118</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5094; 16377</t>
+          <t>5144; 15509</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11981; 30659</t>
+          <t>11985; 29583</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4332; 15047</t>
+          <t>4162; 15182</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6918; 18947</t>
+          <t>6807; 18448</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>13508; 28676</t>
+          <t>13736; 30116</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>8050; 26338</t>
+          <t>7351; 25408</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5844; 29666</t>
+          <t>5349; 28866</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>16050; 44299</t>
+          <t>16450; 46592</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1584; 8338</t>
+          <t>1423; 8395</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>991; 4977</t>
+          <t>966; 5005</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3380; 10886</t>
+          <t>3284; 10900</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>8090; 21298</t>
+          <t>8180; 22024</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>6065; 15854</t>
+          <t>6452; 15584</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>17551; 33592</t>
+          <t>17313; 33141</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>1135; 15120</t>
+          <t>1960; 13537</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3732; 12511</t>
+          <t>3682; 13046</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>7365; 22566</t>
+          <t>7524; 23450</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>4080; 29693</t>
+          <t>4885; 30701</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>18177; 47074</t>
+          <t>17548; 44926</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>18710; 66437</t>
+          <t>16781; 64874</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>49777; 96815</t>
+          <t>50276; 101240</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>67339; 108218</t>
+          <t>65658; 105418</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>125685; 196400</t>
+          <t>124570; 192169</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P70D_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P70D_R-Provincia-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,33%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,66; 5,23</t>
+          <t>0,77; 4,78</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,47</t>
+          <t>0,0; 1,65</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,43; 3,17</t>
+          <t>0,54; 2,83</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,72%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,86; 7,75</t>
+          <t>1,84; 7,78</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,06; 9,23</t>
+          <t>3,0; 9,31</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,89; 7,13</t>
+          <t>3,07; 7,15</t>
         </is>
       </c>
     </row>
@@ -654,12 +654,12 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,6%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,8; 10,21</t>
+          <t>2,95; 10,1</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,63; 15,26</t>
+          <t>5,81; 15,63</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,1; 11,17</t>
+          <t>5,13; 11,19</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>8,54%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,44; 15,36</t>
+          <t>3,73; 12,7</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,07; 11,2</t>
+          <t>5,86; 16,09</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,89; 11,01</t>
+          <t>5,83; 12,05</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>3,57%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,25; 7,35</t>
+          <t>1,65; 8,09</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,9; 4,69</t>
+          <t>1,38; 6,14</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,49; 4,93</t>
+          <t>2,02; 5,74</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>11,03%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6,06; 16,31</t>
+          <t>6,34; 15,94</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7,47; 18,04</t>
+          <t>7,31; 18,03</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7,82; 14,96</t>
+          <t>7,81; 15,28</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,85%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,58; 4,03</t>
+          <t>0,48; 4,17</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,2; 4,24</t>
+          <t>1,13; 3,92</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,17; 3,65</t>
+          <t>1,06; 3,42</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>5,99%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,78; 4,9</t>
+          <t>2,47; 6,46</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>6,45; 16,52</t>
+          <t>6,44; 12,37</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,87; 7,22</t>
+          <t>4,47; 7,72</t>
         </is>
       </c>
     </row>
@@ -949,17 +949,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>5,01%</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,56; 5,15</t>
+          <t>3,49; 5,41</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>4,49; 7,2</t>
+          <t>4,93; 7,15</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3,63; 5,6</t>
+          <t>4,35; 5,87</t>
         </is>
       </c>
     </row>
@@ -1111,17 +1111,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4037</t>
+          <t>4257</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>436</t>
+          <t>468</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4473</t>
+          <t>4726</t>
         </is>
       </c>
     </row>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1287; 10161</t>
+          <t>1565; 9669</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 2125</t>
+          <t>0; 2516</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1461; 10727</t>
+          <t>1930; 10058</t>
         </is>
       </c>
     </row>
@@ -1184,17 +1184,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>10692</t>
+          <t>10564</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>9398</t>
+          <t>9916</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>20090</t>
+          <t>20481</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4587; 19118</t>
+          <t>4727; 19958</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5144; 15509</t>
+          <t>5301; 16466</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11985; 29583</t>
+          <t>13326; 31006</t>
         </is>
       </c>
     </row>
@@ -1257,17 +1257,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>8529</t>
+          <t>8586</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>11636</t>
+          <t>12145</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>20165</t>
+          <t>20732</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4162; 15182</t>
+          <t>4418; 15109</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6807; 18448</t>
+          <t>7149; 19227</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>13736; 30116</t>
+          <t>13975; 30513</t>
         </is>
       </c>
     </row>
@@ -1330,17 +1330,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>14708</t>
+          <t>15596</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>15770</t>
+          <t>17613</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>30478</t>
+          <t>33208</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>7351; 25408</t>
+          <t>7818; 26594</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5349; 28866</t>
+          <t>10511; 28881</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>16450; 46592</t>
+          <t>22676; 46859</t>
         </is>
       </c>
     </row>
@@ -1403,17 +1403,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3883</t>
+          <t>5642</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2373</t>
+          <t>3478</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6256</t>
+          <t>9120</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1423; 8395</t>
+          <t>2247; 11017</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>966; 5005</t>
+          <t>1644; 7305</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3284; 10900</t>
+          <t>5153; 14649</t>
         </is>
       </c>
     </row>
@@ -1476,17 +1476,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>13792</t>
+          <t>14172</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>10424</t>
+          <t>10474</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>24216</t>
+          <t>24646</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>8180; 22024</t>
+          <t>8624; 21690</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>6452; 15584</t>
+          <t>6383; 15749</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>17313; 33141</t>
+          <t>17441; 34149</t>
         </is>
       </c>
     </row>
@@ -1549,17 +1549,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>5511</t>
+          <t>5674</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>7296</t>
+          <t>8229</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>12807</t>
+          <t>13903</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>1960; 13537</t>
+          <t>1875; 16197</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3682; 13046</t>
+          <t>4119; 14247</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>7524; 23450</t>
+          <t>8000; 25711</t>
         </is>
       </c>
     </row>
@@ -1622,17 +1622,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>15751</t>
+          <t>18548</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>26448</t>
+          <t>27396</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>42199</t>
+          <t>45943</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>4885; 30701</t>
+          <t>11200; 29283</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>17548; 44926</t>
+          <t>20166; 38744</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>16781; 64874</t>
+          <t>34264; 59215</t>
         </is>
       </c>
     </row>
@@ -1695,17 +1695,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>76904</t>
+          <t>83039</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>83780</t>
+          <t>89720</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>160684</t>
+          <t>172759</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>50276; 101240</t>
+          <t>67463; 104557</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>65658; 105418</t>
+          <t>74678; 108319</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>124570; 192169</t>
+          <t>149857; 202238</t>
         </is>
       </c>
     </row>
